--- a/NexGen_Tech_Financial_Model_and_DCF_Valuation.xlsx
+++ b/NexGen_Tech_Financial_Model_and_DCF_Valuation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/062d628e8a33ccc6/Documents/Projects/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\omkar\OneDrive\Documents\Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{017AE41E-2AA9-4170-8A34-6A6B6BD90768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CABC62D-E700-4161-BBFE-2C3DCA7D464E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A35E1EFC-E7D2-4244-B9C6-69BD6C11D796}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
   <si>
     <t>NEXGEN TECH PVT LTD — MODEL ASSUMPTIONS &amp; DRIVERS</t>
   </si>
@@ -244,17 +244,99 @@
   </si>
   <si>
     <t>TOTAL NON-CURRENT LIABILITIES</t>
+  </si>
+  <si>
+    <t>NEXGEN TECH - PRO FORMA STATEMENT OF CASH FLOWS (2026 - 2029)</t>
+  </si>
+  <si>
+    <t>Cash Flow Statement Line Item</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+  </si>
+  <si>
+    <t>Net Income (PAT)</t>
+  </si>
+  <si>
+    <t>Add: Non-Cash Depreciation</t>
+  </si>
+  <si>
+    <t>Change in Working Capital (AR &amp; AP)</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM OPERATIONS (CFO)</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+  </si>
+  <si>
+    <t>Capital Expenditures (CapEx)</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM INVESTING (CFI)</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM FINANCING ACTIVITIES</t>
+  </si>
+  <si>
+    <t>Long-Term Debt Repayment / Issuance</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM FINANCING (CFF)</t>
+  </si>
+  <si>
+    <t>NET CHANGE IN CASH BALANCE</t>
+  </si>
+  <si>
+    <t>Beginning Cash Balance</t>
+  </si>
+  <si>
+    <t>ENDING CASH BALANCE</t>
+  </si>
+  <si>
+    <t>NEXGEN TECH - DCF VALUATION &amp; TWO-WAY SENSITIVITY MATRIX</t>
+  </si>
+  <si>
+    <t>VALUATION PARAMETER</t>
+  </si>
+  <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>Base 2029 Forecast EBITDA</t>
+  </si>
+  <si>
+    <t>Effective Tax Rate</t>
+  </si>
+  <si>
+    <t>Weighted Average Cost of Capital (WACC)</t>
+  </si>
+  <si>
+    <t>Terminal Growth Rate (g)</t>
+  </si>
+  <si>
+    <t>IMPLIED ENTERPRISE VALUE</t>
+  </si>
+  <si>
+    <t>TWO-WAY DCF VALUATION SENSITIVITY MATRIX</t>
+  </si>
+  <si>
+    <t>IMPLIED ENTERPRISE VALUE: â‚¹ 1,92,38,543</t>
+  </si>
+  <si>
+    <t>WACC \ Terminal Growth (g)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="5" formatCode="&quot;₹&quot;\ #,##0;&quot;₹&quot;\ \-#,##0"/>
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,8 +454,24 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,6 +508,42 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF141926"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F9DD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7F3FE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEEADB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF9E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E6DD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -440,45 +574,21 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="5" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="5" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="5" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="5" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="5" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="5" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -488,7 +598,7 @@
     <xf numFmtId="9" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="5" fontId="11" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -526,9 +636,50 @@
     <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -874,239 +1025,239 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="47"/>
       <c r="C4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="16">
         <v>0.25</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="16">
         <v>0.35</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="16">
         <v>0.1</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="17">
         <f>CHOOSE($C$4, B7, C7, D7)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="16">
         <v>0.2</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="16">
         <v>0.16</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="16">
         <v>0.25</v>
       </c>
-      <c r="E8" s="25">
-        <f t="shared" ref="E8:E14" si="0">CHOOSE($C$4, B8, C8, D8)</f>
+      <c r="E8" s="17">
+        <f t="shared" ref="E8:E13" si="0">CHOOSE($C$4, B8, C8, D8)</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="16">
         <v>0.25</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="16">
         <v>0.2</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="16">
         <v>0.3</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="17">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="16">
         <v>0.18</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="16">
         <v>0.15</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="16">
         <v>0.22</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="17">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="16">
         <v>0.08</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="16">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="16">
         <v>0.1</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="17">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="18">
         <v>600000</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="18">
         <v>600000</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="18">
         <v>650000</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="19">
         <f t="shared" si="0"/>
         <v>600000</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="16">
         <v>0.25</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="16">
         <v>0.25</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="16">
         <v>0.25</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="17">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="16">
         <v>0.1</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="16">
         <v>0.1</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="16">
         <v>0.1</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="17">
         <f>CHOOSE($C$4, B14, C14, D14)</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="21">
         <v>1000000</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="28">
         <v>1000000</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="28">
         <v>1000000</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="21">
         <f>CHOOSE($C$4, B15,C15,D15)</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="23">
         <v>625000</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="29">
         <v>625000</v>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="29">
         <v>625000</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="23">
         <f>CHOOSE($C$4, B16, C16, D16)</f>
         <v>625000</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="24">
         <v>0.08</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="30">
         <v>0.08</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="30">
         <v>0.08</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="25">
         <f>CHOOSE($C$4, B17, C17, D17)</f>
         <v>0.08</v>
       </c>
@@ -1135,367 +1286,367 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
     </row>
     <row r="2" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="49" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>5000000</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <f>B7 * (1 + Assumptions!$E$7)</f>
         <v>6250000</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <f>C7 * (1 + Assumptions!$E$7)</f>
         <v>7812500</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <f>D7 * (1 + Assumptions!$E$7)</f>
         <v>9765625</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>1000000</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <f>C7*Assumptions!$E$8</f>
         <v>1250000</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <f>D7*Assumptions!$E$8</f>
         <v>1562500</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <f>E7*Assumptions!$E$8</f>
         <v>1953125</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <f>B7-B8</f>
         <v>4000000</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <f>C7-C8</f>
         <v>5000000</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <f t="shared" ref="D9:E9" si="0">D7-D8</f>
         <v>6250000</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <f t="shared" si="0"/>
         <v>7812500</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>1250000</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <f>C7*Assumptions!$E$9</f>
         <v>1562500</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <f>D7*Assumptions!$E$9</f>
         <v>1953125</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <f>E7*Assumptions!$E$9</f>
         <v>2441406.25</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>900000</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <f>C7*Assumptions!$E$10</f>
         <v>1125000</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <f>D7*Assumptions!$E$10</f>
         <v>1406250</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <f>E7*Assumptions!$E$10</f>
         <v>1757812.5</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>400000</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <f>C7*Assumptions!$E$11</f>
         <v>500000</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <f>D7*Assumptions!$E$11</f>
         <v>625000</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <f>E7*Assumptions!$E$11</f>
         <v>781250</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>600000</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <f>Assumptions!$E$12</f>
         <v>600000</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <f>Assumptions!$E$12</f>
         <v>600000</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <f>Assumptions!$E$12</f>
         <v>600000</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <f>SUM(B11:B14)</f>
         <v>3150000</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="6">
         <f>SUM(C11:C14)</f>
         <v>3787500</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <f t="shared" ref="D15:E15" si="1">SUM(D11:D14)</f>
         <v>4584375</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
         <f t="shared" si="1"/>
         <v>5580468.75</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <f>B9-B15</f>
         <v>850000</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <f>C9-C15</f>
         <v>1212500</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <f t="shared" ref="D16:E16" si="2">D9-D15</f>
         <v>1665625</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="6">
         <f t="shared" si="2"/>
         <v>2232031.25</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>100000</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <f>Assumptions!$E$15*Assumptions!$E$14</f>
         <v>100000</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <f>Assumptions!$E$15*Assumptions!$E$14</f>
         <v>100000</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <f>Assumptions!$E$15*Assumptions!$E$14</f>
         <v>100000</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <f>B16-B17</f>
         <v>750000</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="6">
         <f>C16-C17</f>
         <v>1112500</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <f t="shared" ref="D18:E18" si="3">D16-D17</f>
         <v>1565625</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="6">
         <f t="shared" si="3"/>
         <v>2132031.25</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>50000</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <f>Assumptions!$E$16*Assumptions!$E$17</f>
         <v>50000</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <f>Assumptions!$E$16*Assumptions!$E$17</f>
         <v>50000</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <f>Assumptions!$E$16*Assumptions!$E$17</f>
         <v>50000</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="6">
         <f>B18-B19</f>
         <v>700000</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="6">
         <f>C18-C19</f>
         <v>1062500</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="6">
         <f t="shared" ref="D20:E20" si="4">D18-D19</f>
         <v>1515625</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="6">
         <f t="shared" si="4"/>
         <v>2082031.25</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <f>B20*0.25</f>
         <v>175000</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <f>IF(C20&gt;0,C20*Assumptions!$E$13,0)</f>
         <v>265625</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="5">
         <f>IF(D20&gt;0,D20*Assumptions!$E$13,0)</f>
         <v>378906.25</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <f>IF(E20&gt;0,E20*Assumptions!$E$13,0)</f>
         <v>520507.8125</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="10">
         <f>B20-B21</f>
         <v>525000</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="10">
         <f>C20-C21</f>
         <v>796875</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="10">
         <f t="shared" ref="D22:E22" si="5">D20-D21</f>
         <v>1136718.75</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="10">
         <f t="shared" si="5"/>
         <v>1561523.4375</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -1516,475 +1667,475 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="55" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>1500000</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="11">
         <f>C32-C15-C8</f>
         <v>2520162.0958904112</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="11">
         <f>D32-D15-D8</f>
         <v>3654141.1198630137</v>
       </c>
-      <c r="E7" s="16">
-        <f t="shared" ref="D7:E7" si="0">E32-E15-E8</f>
+      <c r="E7" s="11">
+        <f t="shared" ref="E7" si="0">E32-E15-E8</f>
         <v>5187239.8998287665</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>616438</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="11">
         <f>('Income statement '!C7/365)*30</f>
         <v>513698.63013698626</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="11">
         <f>('Income statement '!D7/365)*30</f>
         <v>642123.28767123283</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="11">
         <f>('Income statement '!E7/365)*30</f>
         <v>802654.10958904109</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <f>SUM(B7:B8)</f>
         <v>2116438</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="13">
         <f>SUM(C7:C8)</f>
         <v>3033860.7260273974</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="13">
         <f t="shared" ref="D9:E9" si="1">SUM(D7:D8)</f>
         <v>4296264.4075342463</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="13">
         <f t="shared" si="1"/>
         <v>5989894.0094178077</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="7"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>1000000</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="11">
         <f>B12</f>
         <v>1000000</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="11">
         <f t="shared" ref="D12:E12" si="2">C12</f>
         <v>1000000</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="11">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>100000</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="11">
         <f>B13+'Income statement '!C17</f>
         <v>200000</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="11">
         <f>C13+'Income statement '!D17</f>
         <v>300000</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="11">
         <f>D13+'Income statement '!E17</f>
         <v>400000</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <f>B12-B13</f>
         <v>900000</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="11">
         <f>C12-C13</f>
         <v>800000</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="11">
         <f t="shared" ref="D14:E14" si="3">D12-D13</f>
         <v>700000</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="11">
         <f t="shared" si="3"/>
         <v>600000</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <f>B14</f>
         <v>900000</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="11">
         <f>C14</f>
         <v>800000</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="11">
         <f t="shared" ref="D15:E15" si="4">D14</f>
         <v>700000</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="11">
         <f t="shared" si="4"/>
         <v>600000</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="10">
         <f>B9+B14</f>
         <v>3016438</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="12">
         <f>C9+C15</f>
         <v>3833860.7260273974</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="12">
         <f t="shared" ref="D16:E16" si="5">D9+D15</f>
         <v>4996264.4075342463</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="12">
         <f t="shared" si="5"/>
         <v>6589894.0094178077</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="5"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="7"/>
+      <c r="B18" s="5"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="7"/>
+      <c r="B19" s="5"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>82192</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="11">
         <f>('Income statement '!C8/365)*30</f>
         <v>102739.72602739726</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="11">
         <f>('Income statement '!D8/365)*30</f>
         <v>128424.65753424657</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="11">
         <f>('Income statement '!E8/365)*30</f>
         <v>160530.82191780821</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="6">
         <f>B20</f>
         <v>82192</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="13">
         <f>C20</f>
         <v>102739.72602739726</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="13">
         <f t="shared" ref="D21:E21" si="6">D20</f>
         <v>128424.65753424657</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="13">
         <f t="shared" si="6"/>
         <v>160530.82191780821</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="5"/>
     </row>
     <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="7"/>
+      <c r="B23" s="5"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="5">
         <v>625000</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="11">
         <f>B24</f>
         <v>625000</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="11">
         <f t="shared" ref="D24:E24" si="7">C24</f>
         <v>625000</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="11">
         <f t="shared" si="7"/>
         <v>625000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="5">
         <f>B24</f>
         <v>625000</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="11">
         <f>C24</f>
         <v>625000</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="11">
         <f t="shared" ref="D25:E25" si="8">D24</f>
         <v>625000</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="11">
         <f t="shared" si="8"/>
         <v>625000</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <f>B24+B21</f>
         <v>707192</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="13">
         <f>C21+C25</f>
         <v>727739.72602739721</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D26" s="13">
         <f t="shared" ref="D26:E26" si="9">D21+D25</f>
         <v>753424.65753424657</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="13">
         <f t="shared" si="9"/>
         <v>785530.82191780815</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="5"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="7"/>
+      <c r="B28" s="5"/>
     </row>
     <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="5">
         <v>1000000</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="11">
         <f>B29</f>
         <v>1000000</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="11">
         <f t="shared" ref="D29:E29" si="10">C29</f>
         <v>1000000</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="11">
         <f t="shared" si="10"/>
         <v>1000000</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="5">
         <v>1309246</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="11">
         <f>B30+'Income statement '!C22</f>
         <v>2106121</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="11">
         <f>C30+'Income statement '!D22</f>
         <v>3242839.75</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="11">
         <f>D30+'Income statement '!E22</f>
         <v>4804363.1875</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="6">
         <f>SUM(B29:B30)</f>
         <v>2309246</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="11">
         <f>SUM(C29:C30)</f>
         <v>3106121</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="11">
         <f t="shared" ref="D31:E31" si="11">SUM(D29:D30)</f>
         <v>4242839.75</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="11">
         <f t="shared" si="11"/>
         <v>5804363.1875</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="10">
         <f>B26+B31</f>
         <v>3016438</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="12">
         <f>C26+C31</f>
         <v>3833860.7260273974</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="12">
         <f t="shared" ref="D32:E32" si="12">D26+D31</f>
         <v>4996264.4075342463</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="12">
         <f t="shared" si="12"/>
         <v>6589894.0094178077</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:E2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1992,18 +2143,500 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E1F010-C4FB-4CC3-82AF-6E4EB4905CC1}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="67.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="40">
+        <f>'Income statement '!B11</f>
+        <v>1250000</v>
+      </c>
+      <c r="C5" s="40">
+        <f>'Income statement '!C11</f>
+        <v>1562500</v>
+      </c>
+      <c r="D5" s="40">
+        <f>'Income statement '!D11</f>
+        <v>1953125</v>
+      </c>
+      <c r="E5" s="40">
+        <f>'Income statement '!E11</f>
+        <v>2441406.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="40">
+        <f>'Income statement '!B7</f>
+        <v>5000000</v>
+      </c>
+      <c r="C6" s="40">
+        <f>'Income statement '!C7</f>
+        <v>6250000</v>
+      </c>
+      <c r="D6" s="40">
+        <f>'Income statement '!D7</f>
+        <v>7812500</v>
+      </c>
+      <c r="E6" s="40">
+        <f>'Income statement '!E7</f>
+        <v>9765625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="40">
+        <v>0</v>
+      </c>
+      <c r="C7" s="40">
+        <v>123288</v>
+      </c>
+      <c r="D7" s="40">
+        <v>-102739</v>
+      </c>
+      <c r="E7" s="40">
+        <v>-128425</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="41">
+        <f>SUM(B5:B7)</f>
+        <v>6250000</v>
+      </c>
+      <c r="C8" s="41">
+        <f>SUM(C5:C7)</f>
+        <v>7935788</v>
+      </c>
+      <c r="D8" s="41">
+        <f>SUM(D5:D7)</f>
+        <v>9662886</v>
+      </c>
+      <c r="E8" s="41">
+        <f>SUM(E5:E7)</f>
+        <v>12078606.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="40">
+        <v>0</v>
+      </c>
+      <c r="C11" s="40">
+        <v>0</v>
+      </c>
+      <c r="D11" s="40">
+        <v>0</v>
+      </c>
+      <c r="E11" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="56">
+        <v>0</v>
+      </c>
+      <c r="C12" s="56">
+        <v>0</v>
+      </c>
+      <c r="D12" s="56">
+        <v>0</v>
+      </c>
+      <c r="E12" s="56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="40">
+        <v>0</v>
+      </c>
+      <c r="C15" s="40">
+        <v>0</v>
+      </c>
+      <c r="D15" s="40">
+        <v>0</v>
+      </c>
+      <c r="E15" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="56">
+        <v>0</v>
+      </c>
+      <c r="C16" s="56">
+        <v>0</v>
+      </c>
+      <c r="D16" s="56">
+        <v>0</v>
+      </c>
+      <c r="E16" s="56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="42">
+        <f>B8+B12+B16</f>
+        <v>6250000</v>
+      </c>
+      <c r="C18" s="42">
+        <f>C8+C12+C16</f>
+        <v>7935788</v>
+      </c>
+      <c r="D18" s="42">
+        <f>D8+D12+D16</f>
+        <v>9662886</v>
+      </c>
+      <c r="E18" s="42">
+        <f>E8+E12+E16</f>
+        <v>12078606.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="40">
+        <v>0</v>
+      </c>
+      <c r="C19" s="40">
+        <f>B20</f>
+        <v>6250000</v>
+      </c>
+      <c r="D19" s="40">
+        <f>C20</f>
+        <v>14185788</v>
+      </c>
+      <c r="E19" s="40">
+        <f>D20</f>
+        <v>23848674</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="43">
+        <f>B18+B19</f>
+        <v>6250000</v>
+      </c>
+      <c r="C20" s="43">
+        <f>C18+C19</f>
+        <v>14185788</v>
+      </c>
+      <c r="D20" s="43">
+        <f>D18+D19</f>
+        <v>23848674</v>
+      </c>
+      <c r="E20" s="43">
+        <f>E18+E19</f>
+        <v>35927280.25</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27EA545A-387F-4AE1-B78E-057214D5B253}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="62.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="40">
+        <f>'Income statement '!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="36">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="36">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="36">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="44">
+        <v>19238543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="39">
+        <v>0.02</v>
+      </c>
+      <c r="C14" s="39">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D14" s="39">
+        <v>0.03</v>
+      </c>
+      <c r="E14" s="39">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F14" s="39">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="39"/>
+      <c r="B15" s="45">
+        <f>ROUND(19238543 * (((1+B$14)/($A15-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-66681164</v>
+      </c>
+      <c r="C15" s="45">
+        <f>ROUND(19238543 * (((1+C$14)/($A15-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-53606426</v>
+      </c>
+      <c r="D15" s="45">
+        <f>ROUND(19238543 * (((1+D$14)/($A15-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-44889934</v>
+      </c>
+      <c r="E15" s="45">
+        <f>ROUND(19238543 * (((1+E$14)/($A15-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-38663868</v>
+      </c>
+      <c r="F15" s="45">
+        <f>ROUND(19238543 * (((1+F$14)/($A15-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-33994319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="39"/>
+      <c r="B16" s="45">
+        <f>ROUND(19238543 * (((1+B$14)/($A16-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-66681164</v>
+      </c>
+      <c r="C16" s="45">
+        <f>ROUND(19238543 * (((1+C$14)/($A16-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-53606426</v>
+      </c>
+      <c r="D16" s="45">
+        <f>ROUND(19238543 * (((1+D$14)/($A16-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-44889934</v>
+      </c>
+      <c r="E16" s="45">
+        <f>ROUND(19238543 * (((1+E$14)/($A16-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-38663868</v>
+      </c>
+      <c r="F16" s="45">
+        <f>ROUND(19238543 * (((1+F$14)/($A16-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-33994319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="39"/>
+      <c r="B17" s="46">
+        <f>ROUND(19238543 * (((1+B$14)/($A17-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-66681164</v>
+      </c>
+      <c r="C17" s="46">
+        <f>ROUND(19238543 * (((1+C$14)/($A17-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-53606426</v>
+      </c>
+      <c r="D17" s="44">
+        <f>ROUND(19238543 * (((1+D$14)/($A17-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-44889934</v>
+      </c>
+      <c r="E17" s="45">
+        <f>ROUND(19238543 * (((1+E$14)/($A17-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-38663868</v>
+      </c>
+      <c r="F17" s="45">
+        <f>ROUND(19238543 * (((1+F$14)/($A17-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-33994319</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="39"/>
+      <c r="B18" s="46">
+        <f>ROUND(19238543 * (((1+B$14)/($A18-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-66681164</v>
+      </c>
+      <c r="C18" s="46">
+        <f>ROUND(19238543 * (((1+C$14)/($A18-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-53606426</v>
+      </c>
+      <c r="D18" s="46">
+        <f>ROUND(19238543 * (((1+D$14)/($A18-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-44889934</v>
+      </c>
+      <c r="E18" s="45">
+        <f>ROUND(19238543 * (((1+E$14)/($A18-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-38663868</v>
+      </c>
+      <c r="F18" s="45">
+        <f>ROUND(19238543 * (((1+F$14)/($A18-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-33994319</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="39"/>
+      <c r="B19" s="46">
+        <f>ROUND(19238543 * (((1+B$14)/($A19-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-66681164</v>
+      </c>
+      <c r="C19" s="46">
+        <f>ROUND(19238543 * (((1+C$14)/($A19-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-53606426</v>
+      </c>
+      <c r="D19" s="46">
+        <f>ROUND(19238543 * (((1+D$14)/($A19-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-44889934</v>
+      </c>
+      <c r="E19" s="45">
+        <f>ROUND(19238543 * (((1+E$14)/($A19-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-38663868</v>
+      </c>
+      <c r="F19" s="45">
+        <f>ROUND(19238543 * (((1+F$14)/($A19-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
+        <v>-33994319</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/NexGen_Tech_Financial_Model_and_DCF_Valuation.xlsx
+++ b/NexGen_Tech_Financial_Model_and_DCF_Valuation.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\omkar\OneDrive\Documents\Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/062d628e8a33ccc6/Documents/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CABC62D-E700-4161-BBFE-2C3DCA7D464E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{621E777F-59DC-400F-96CE-C1E46ED5364A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A35E1EFC-E7D2-4244-B9C6-69BD6C11D796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{A35E1EFC-E7D2-4244-B9C6-69BD6C11D796}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="105">
   <si>
     <t>NEXGEN TECH PVT LTD — MODEL ASSUMPTIONS &amp; DRIVERS</t>
   </si>
@@ -246,46 +246,49 @@
     <t>TOTAL NON-CURRENT LIABILITIES</t>
   </si>
   <si>
-    <t>NEXGEN TECH - PRO FORMA STATEMENT OF CASH FLOWS (2026 - 2029)</t>
-  </si>
-  <si>
-    <t>Cash Flow Statement Line Item</t>
-  </si>
-  <si>
-    <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
-  </si>
-  <si>
-    <t>Net Income (PAT)</t>
-  </si>
-  <si>
-    <t>Add: Non-Cash Depreciation</t>
-  </si>
-  <si>
-    <t>Change in Working Capital (AR &amp; AP)</t>
-  </si>
-  <si>
-    <t>CASH FLOW FROM OPERATIONS (CFO)</t>
-  </si>
-  <si>
-    <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+    <t>NEXGEN TECH PVT LTD — PRO FORMA CASH FLOW STATEMENT</t>
+  </si>
+  <si>
+    <t>CASH FLOW LINE ITEM</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM OPERATING ACTIVITIES (CFO):</t>
+  </si>
+  <si>
+    <t>Net Income (Profit After Tax)</t>
+  </si>
+  <si>
+    <t>(+) Depreciation Add-Back</t>
+  </si>
+  <si>
+    <t>(-) Increase in Accounts Receivable (AR)</t>
+  </si>
+  <si>
+    <t>(+) Increase in Accounts Payable (AP)</t>
+  </si>
+  <si>
+    <t>NET CASH FROM OPERATING ACTIVITIES (CFO)</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM INVESTING ACTIVITIES (CFI):</t>
   </si>
   <si>
     <t>Capital Expenditures (CapEx)</t>
   </si>
   <si>
-    <t>CASH FLOW FROM INVESTING (CFI)</t>
-  </si>
-  <si>
-    <t>CASH FLOW FROM FINANCING ACTIVITIES</t>
-  </si>
-  <si>
-    <t>Long-Term Debt Repayment / Issuance</t>
-  </si>
-  <si>
-    <t>CASH FLOW FROM FINANCING (CFF)</t>
-  </si>
-  <si>
-    <t>NET CHANGE IN CASH BALANCE</t>
+    <t>NET CASH FROM INVESTING ACTIVITIES (CFI)</t>
+  </si>
+  <si>
+    <t>CASH FLOW FROM FINANCING ACTIVITIES (CFF):</t>
+  </si>
+  <si>
+    <t>Debt Issued / (Repaid)</t>
+  </si>
+  <si>
+    <t>NET CASH FROM FINANCING ACTIVITIES (CFF)</t>
+  </si>
+  <si>
+    <t>NET CHANGE IN CASH</t>
   </si>
   <si>
     <t>Beginning Cash Balance</t>
@@ -294,49 +297,78 @@
     <t>ENDING CASH BALANCE</t>
   </si>
   <si>
-    <t>NEXGEN TECH - DCF VALUATION &amp; TWO-WAY SENSITIVITY MATRIX</t>
-  </si>
-  <si>
-    <t>VALUATION PARAMETER</t>
-  </si>
-  <si>
-    <t>VALUE</t>
-  </si>
-  <si>
-    <t>Base 2029 Forecast EBITDA</t>
-  </si>
-  <si>
-    <t>Effective Tax Rate</t>
+    <t>NEXGEN TECH PVT LTD — DISCOUNTED CASH FLOW (DCF) VALUATION</t>
   </si>
   <si>
     <t>Weighted Average Cost of Capital (WACC)</t>
   </si>
   <si>
-    <t>Terminal Growth Rate (g)</t>
-  </si>
-  <si>
-    <t>IMPLIED ENTERPRISE VALUE</t>
-  </si>
-  <si>
-    <t>TWO-WAY DCF VALUATION SENSITIVITY MATRIX</t>
-  </si>
-  <si>
-    <t>IMPLIED ENTERPRISE VALUE: â‚¹ 1,92,38,543</t>
-  </si>
-  <si>
-    <t>WACC \ Terminal Growth (g)</t>
+    <t>Perpetual Terminal Growth Rate (g)</t>
+  </si>
+  <si>
+    <t>FCFF LINE ITEM</t>
+  </si>
+  <si>
+    <t>Less: Taxes on EBIT</t>
+  </si>
+  <si>
+    <t>NOPAT (Net Operating Profit After Tax)</t>
+  </si>
+  <si>
+    <t>(-) Change in Net Working Capital (ΔΔNWC)</t>
+  </si>
+  <si>
+    <t>(-) CapEx</t>
+  </si>
+  <si>
+    <t>UNLEVERED FREE CASH FLOW (FCFF)</t>
+  </si>
+  <si>
+    <t>Discount Period (tt)</t>
+  </si>
+  <si>
+    <t>Discount Factor</t>
+  </si>
+  <si>
+    <t>PV of Discrete FCFF</t>
+  </si>
+  <si>
+    <t>VALUATION SUMMARY:</t>
+  </si>
+  <si>
+    <t>Cumulative PV of 3-Yr Cash Flows</t>
+  </si>
+  <si>
+    <t>Terminal Value (Gordon Growth)</t>
+  </si>
+  <si>
+    <t>PV of Terminal Value</t>
+  </si>
+  <si>
+    <t>IMPLIED ENTERPRISE VALUE (EV)</t>
+  </si>
+  <si>
+    <t>(+) Cash &amp; Cash Equivalents</t>
+  </si>
+  <si>
+    <t>(-) Total Debt</t>
+  </si>
+  <si>
+    <t>IMPLIED EQUITY VALUE</t>
+  </si>
+  <si>
+    <t>2-WAY ENTERPRISE VALUE SENSITIVITY MATRIX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="5" formatCode="&quot;₹&quot;\ #,##0;&quot;₹&quot;\ \-#,##0"/>
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,14 +397,6 @@
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -456,8 +480,22 @@
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF101010"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -465,13 +503,20 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF101010"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF004F88"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -510,42 +555,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF141926"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F9DD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7F3FE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEEADB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF9E6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E6DD"/>
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -568,118 +583,427 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="5" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="5" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="5" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="5" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="5" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="5" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="5" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="10" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="8" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="8" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="5" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="5" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="5" fontId="11" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="5" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="5" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="5" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="5" fontId="11" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -697,6 +1021,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1016,6 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA0D454-D7FA-4565-B820-209BBC74B17F}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1025,247 +1354,249 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="82"/>
     </row>
     <row r="2" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="82"/>
+      <c r="B2" s="82"/>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="83">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="19.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
+      <c r="B4" s="81"/>
+      <c r="C4" s="83"/>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="5">
         <v>0.25</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="5">
         <v>0.35</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="5">
         <v>0.1</v>
       </c>
-      <c r="E7" s="17">
-        <f>CHOOSE($C$4, B7, C7, D7)</f>
+      <c r="E7" s="6">
+        <f t="shared" ref="E7:E14" si="0">CHOOSE($C$3, B7, C7, D7)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="5">
         <v>0.2</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="5">
         <v>0.16</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="5">
         <v>0.25</v>
       </c>
-      <c r="E8" s="17">
-        <f t="shared" ref="E8:E13" si="0">CHOOSE($C$4, B8, C8, D8)</f>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="5">
         <v>0.25</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="5">
         <v>0.2</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="5">
         <v>0.3</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="6">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="5">
         <v>0.18</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="5">
         <v>0.15</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="5">
         <v>0.22</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="6">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="5">
         <v>0.08</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="5">
         <v>0.1</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="6">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="7">
         <v>600000</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="7">
         <v>600000</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="7">
         <v>650000</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="8">
         <f t="shared" si="0"/>
         <v>600000</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="5">
         <v>0.25</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="5">
         <v>0.25</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="5">
         <v>0.25</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="6">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="5">
         <v>0.1</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="5">
         <v>0.1</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="5">
         <v>0.1</v>
       </c>
-      <c r="E14" s="17">
-        <f>CHOOSE($C$4, B14, C14, D14)</f>
+      <c r="E14" s="6">
+        <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="10">
         <v>1000000</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="17">
         <v>1000000</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="17">
         <v>1000000</v>
       </c>
-      <c r="E15" s="21">
-        <f>CHOOSE($C$4, B15,C15,D15)</f>
+      <c r="E15" s="10">
+        <f>CHOOSE($C$3, B15,C15,D15)</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="12">
         <v>625000</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="18">
         <v>625000</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="18">
         <v>625000</v>
       </c>
-      <c r="E16" s="23">
-        <f>CHOOSE($C$4, B16, C16, D16)</f>
+      <c r="E16" s="12">
+        <f>CHOOSE($C$3, B16, C16, D16)</f>
         <v>625000</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="13">
         <v>0.08</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="19">
         <v>0.08</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="19">
         <v>0.08</v>
       </c>
-      <c r="E17" s="25">
-        <f>CHOOSE($C$4, B17, C17, D17)</f>
+      <c r="E17" s="14">
+        <f>CHOOSE($C$3, B17, C17, D17)</f>
         <v>0.08</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -1276,373 +1607,382 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966350FB-ABA2-472C-92E9-2AEB46D08C8B}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
     </row>
     <row r="2" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-    </row>
+      <c r="A2" s="92"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="92"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="49" t="s">
+      <c r="E5" s="84" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="51"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="87"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="85"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="40">
         <v>5000000</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="42">
         <f>B7 * (1 + Assumptions!$E$7)</f>
         <v>6250000</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="42">
         <f>C7 * (1 + Assumptions!$E$7)</f>
         <v>7812500</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="42">
         <f>D7 * (1 + Assumptions!$E$7)</f>
         <v>9765625</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="41">
         <v>1000000</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="41">
         <f>C7*Assumptions!$E$8</f>
         <v>1250000</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="41">
         <f>D7*Assumptions!$E$8</f>
         <v>1562500</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="41">
         <f>E7*Assumptions!$E$8</f>
         <v>1953125</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="33">
         <f>B7-B8</f>
         <v>4000000</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="33">
         <f>C7-C8</f>
         <v>5000000</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="33">
         <f t="shared" ref="D9:E9" si="0">D7-D8</f>
         <v>6250000</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="33">
         <f t="shared" si="0"/>
         <v>7812500</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="40">
         <v>1250000</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="40">
         <f>C7*Assumptions!$E$9</f>
         <v>1562500</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="40">
         <f>D7*Assumptions!$E$9</f>
         <v>1953125</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="40">
         <f>E7*Assumptions!$E$9</f>
         <v>2441406.25</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="40">
         <v>900000</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="40">
         <f>C7*Assumptions!$E$10</f>
         <v>1125000</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="40">
         <f>D7*Assumptions!$E$10</f>
         <v>1406250</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="40">
         <f>E7*Assumptions!$E$10</f>
         <v>1757812.5</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="40">
         <v>400000</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="40">
         <f>C7*Assumptions!$E$11</f>
         <v>500000</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="40">
         <f>D7*Assumptions!$E$11</f>
         <v>625000</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="40">
         <f>E7*Assumptions!$E$11</f>
         <v>781250</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="41">
         <v>600000</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="41">
         <f>Assumptions!$E$12</f>
         <v>600000</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="41">
         <f>Assumptions!$E$12</f>
         <v>600000</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="41">
         <f>Assumptions!$E$12</f>
         <v>600000</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="33">
         <f>SUM(B11:B14)</f>
         <v>3150000</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="33">
         <f>SUM(C11:C14)</f>
         <v>3787500</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="33">
         <f t="shared" ref="D15:E15" si="1">SUM(D11:D14)</f>
         <v>4584375</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="33">
         <f t="shared" si="1"/>
         <v>5580468.75</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="38">
         <f>B9-B15</f>
         <v>850000</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="38">
         <f>C9-C15</f>
         <v>1212500</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="38">
         <f t="shared" ref="D16:E16" si="2">D9-D15</f>
         <v>1665625</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="38">
         <f t="shared" si="2"/>
         <v>2232031.25</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="46">
         <v>100000</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="46">
         <f>Assumptions!$E$15*Assumptions!$E$14</f>
         <v>100000</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="46">
         <f>Assumptions!$E$15*Assumptions!$E$14</f>
         <v>100000</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="46">
         <f>Assumptions!$E$15*Assumptions!$E$14</f>
         <v>100000</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="38">
         <f>B16-B17</f>
         <v>750000</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="38">
         <f>C16-C17</f>
         <v>1112500</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="38">
         <f t="shared" ref="D18:E18" si="3">D16-D17</f>
         <v>1565625</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="38">
         <f t="shared" si="3"/>
         <v>2132031.25</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="46">
         <v>50000</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="46">
         <f>Assumptions!$E$16*Assumptions!$E$17</f>
         <v>50000</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="46">
         <f>Assumptions!$E$16*Assumptions!$E$17</f>
         <v>50000</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="46">
         <f>Assumptions!$E$16*Assumptions!$E$17</f>
         <v>50000</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="38">
         <f>B18-B19</f>
         <v>700000</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="38">
         <f>C18-C19</f>
         <v>1062500</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="38">
         <f t="shared" ref="D20:E20" si="4">D18-D19</f>
         <v>1515625</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="38">
         <f t="shared" si="4"/>
         <v>2082031.25</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="46">
         <f>B20*0.25</f>
         <v>175000</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="46">
         <f>IF(C20&gt;0,C20*Assumptions!$E$13,0)</f>
         <v>265625</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="46">
         <f>IF(D20&gt;0,D20*Assumptions!$E$13,0)</f>
         <v>378906.25</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="46">
         <f>IF(E20&gt;0,E20*Assumptions!$E$13,0)</f>
         <v>520507.8125</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="48">
         <f>B20-B21</f>
         <v>525000</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="48">
         <f>C20-C21</f>
         <v>796875</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="48">
         <f t="shared" ref="D22:E22" si="5">D20-D21</f>
         <v>1136718.75</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="49">
         <f t="shared" si="5"/>
         <v>1561523.4375</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:D3"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="A1:D2"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
@@ -1657,7 +1997,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52AED7B3-9457-4182-B42E-7C38355DC4AC}">
-  <dimension ref="A1:G32"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -1667,463 +2008,502 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54" t="s">
+      <c r="A2" s="93"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B4" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C4" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E4" s="95" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="94"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B8" s="40">
         <v>1500000</v>
       </c>
-      <c r="C7" s="11">
-        <f>C32-C15-C8</f>
-        <v>2520162.0958904112</v>
-      </c>
-      <c r="D7" s="11">
-        <f>D32-D15-D8</f>
-        <v>3654141.1198630137</v>
-      </c>
-      <c r="E7" s="11">
-        <f t="shared" ref="E7" si="0">E32-E15-E8</f>
-        <v>5187239.8998287665</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="53">
+        <f>C33-C16-C9</f>
+        <v>2263312.780821918</v>
+      </c>
+      <c r="D8" s="53">
+        <f>D33-D16-D9</f>
+        <v>3333079.476027397</v>
+      </c>
+      <c r="E8" s="53">
+        <f t="shared" ref="E8" si="0">E33-E16-E9</f>
+        <v>4785912.8450342454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B9" s="40">
         <v>616438</v>
       </c>
-      <c r="C8" s="11">
-        <f>('Income statement '!C7/365)*30</f>
-        <v>513698.63013698626</v>
-      </c>
-      <c r="D8" s="11">
-        <f>('Income statement '!D7/365)*30</f>
-        <v>642123.28767123283</v>
-      </c>
-      <c r="E8" s="11">
-        <f>('Income statement '!E7/365)*30</f>
-        <v>802654.10958904109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="C9" s="53">
+        <f>('Income statement '!C7/365)*45</f>
+        <v>770547.94520547939</v>
+      </c>
+      <c r="D9" s="53">
+        <f>('Income statement '!D7/365)*45</f>
+        <v>963184.93150684924</v>
+      </c>
+      <c r="E9" s="53">
+        <f>('Income statement '!E7/365)*45</f>
+        <v>1203981.1643835618</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="6">
-        <f>SUM(B7:B8)</f>
+      <c r="B10" s="33">
+        <f>SUM(B8:B9)</f>
         <v>2116438</v>
       </c>
-      <c r="C9" s="13">
-        <f>SUM(C7:C8)</f>
+      <c r="C10" s="25">
+        <f>SUM(C8:C9)</f>
         <v>3033860.7260273974</v>
       </c>
-      <c r="D9" s="13">
-        <f t="shared" ref="D9:E9" si="1">SUM(D7:D8)</f>
+      <c r="D10" s="25">
+        <f t="shared" ref="D10:E10" si="1">SUM(D8:D9)</f>
         <v>4296264.4075342463</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E10" s="25">
         <f t="shared" si="1"/>
         <v>5989894.0094178077</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="5"/>
-    </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="40">
         <v>1000000</v>
       </c>
-      <c r="C12" s="11">
-        <f>B12</f>
+      <c r="C13" s="53">
+        <f>B13</f>
         <v>1000000</v>
       </c>
-      <c r="D12" s="11">
-        <f t="shared" ref="D12:E12" si="2">C12</f>
+      <c r="D13" s="53">
+        <f t="shared" ref="D13:E13" si="2">C13</f>
         <v>1000000</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E13" s="53">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B14" s="40">
         <v>100000</v>
       </c>
-      <c r="C13" s="11">
-        <f>B13+'Income statement '!C17</f>
+      <c r="C14" s="53">
+        <f>B14+'Income statement '!C17</f>
         <v>200000</v>
       </c>
-      <c r="D13" s="11">
-        <f>C13+'Income statement '!D17</f>
+      <c r="D14" s="53">
+        <f>C14+'Income statement '!D17</f>
         <v>300000</v>
       </c>
-      <c r="E13" s="11">
-        <f>D13+'Income statement '!E17</f>
+      <c r="E14" s="53">
+        <f>D14+'Income statement '!E17</f>
         <v>400000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="5">
-        <f>B12-B13</f>
+      <c r="B15" s="40">
+        <f>B13-B14</f>
         <v>900000</v>
       </c>
-      <c r="C14" s="11">
-        <f>C12-C13</f>
+      <c r="C15" s="53">
+        <f>C13-C14</f>
         <v>800000</v>
       </c>
-      <c r="D14" s="11">
-        <f t="shared" ref="D14:E14" si="3">D12-D13</f>
+      <c r="D15" s="53">
+        <f t="shared" ref="D15:E15" si="3">D13-D14</f>
         <v>700000</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E15" s="53">
         <f t="shared" si="3"/>
         <v>600000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="16" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="6">
-        <f>B14</f>
+      <c r="B16" s="38">
+        <f>B15</f>
         <v>900000</v>
       </c>
-      <c r="C15" s="11">
-        <f>C14</f>
+      <c r="C16" s="60">
+        <f>C15</f>
         <v>800000</v>
       </c>
-      <c r="D15" s="11">
-        <f t="shared" ref="D15:E15" si="4">D14</f>
+      <c r="D16" s="60">
+        <f t="shared" ref="D16:E16" si="4">D15</f>
         <v>700000</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E16" s="60">
         <f t="shared" si="4"/>
         <v>600000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+    <row r="17" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="10">
-        <f>B9+B14</f>
+      <c r="B17" s="48">
+        <f>B10+B15</f>
         <v>3016438</v>
       </c>
-      <c r="C16" s="12">
-        <f>C9+C15</f>
+      <c r="C17" s="58">
+        <f>C10+C16</f>
         <v>3833860.7260273974</v>
       </c>
-      <c r="D16" s="12">
-        <f t="shared" ref="D16:E16" si="5">D9+D15</f>
+      <c r="D17" s="58">
+        <f t="shared" ref="D17:E17" si="5">D10+D16</f>
         <v>4996264.4075342463</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E17" s="59">
         <f t="shared" si="5"/>
         <v>6589894.0094178077</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="5"/>
-    </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="78"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="32"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="36"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B21" s="46">
         <v>82192</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C21" s="71">
         <f>('Income statement '!C8/365)*30</f>
         <v>102739.72602739726</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D21" s="71">
         <f>('Income statement '!D8/365)*30</f>
         <v>128424.65753424657</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E21" s="53">
         <f>('Income statement '!E8/365)*30</f>
         <v>160530.82191780821</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="6">
-        <f>B20</f>
+      <c r="B22" s="33">
+        <f>B21</f>
         <v>82192</v>
       </c>
-      <c r="C21" s="13">
-        <f>C20</f>
+      <c r="C22" s="25">
+        <f>C21</f>
         <v>102739.72602739726</v>
       </c>
-      <c r="D21" s="13">
-        <f t="shared" ref="D21:E21" si="6">D20</f>
+      <c r="D22" s="25">
+        <f t="shared" ref="D22:E22" si="6">D21</f>
         <v>128424.65753424657</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E22" s="25">
         <f t="shared" si="6"/>
         <v>160530.82191780821</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="5"/>
-    </row>
     <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="11"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="5"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="B24" s="36"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B25" s="46">
         <v>625000</v>
       </c>
-      <c r="C24" s="11">
-        <f>B24</f>
+      <c r="C25" s="52">
+        <f>B25</f>
         <v>625000</v>
       </c>
-      <c r="D24" s="11">
-        <f t="shared" ref="D24:E24" si="7">C24</f>
+      <c r="D25" s="53">
+        <f t="shared" ref="D25:E25" si="7">C25</f>
         <v>625000</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E25" s="71">
         <f t="shared" si="7"/>
         <v>625000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="5">
-        <f>B24</f>
+      <c r="B26" s="32">
+        <f>B25</f>
         <v>625000</v>
       </c>
-      <c r="C25" s="11">
-        <f>C24</f>
+      <c r="C26" s="23">
+        <f>C25</f>
         <v>625000</v>
       </c>
-      <c r="D25" s="11">
-        <f t="shared" ref="D25:E25" si="8">D24</f>
+      <c r="D26" s="23">
+        <f t="shared" ref="D26:E26" si="8">D25</f>
         <v>625000</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E26" s="23">
         <f t="shared" si="8"/>
         <v>625000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="6">
-        <f>B24+B21</f>
+      <c r="B27" s="33">
+        <f>B25+B22</f>
         <v>707192</v>
       </c>
-      <c r="C26" s="13">
-        <f>C21+C25</f>
+      <c r="C27" s="25">
+        <f>C22+C26</f>
         <v>727739.72602739721</v>
       </c>
-      <c r="D26" s="13">
-        <f t="shared" ref="D26:E26" si="9">D21+D25</f>
+      <c r="D27" s="25">
+        <f t="shared" ref="D27:E27" si="9">D22+D26</f>
         <v>753424.65753424657</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E27" s="25">
         <f t="shared" si="9"/>
         <v>785530.82191780815</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="5"/>
-    </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="11"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="36"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B30" s="80">
         <v>1000000</v>
       </c>
-      <c r="C29" s="11">
-        <f>B29</f>
+      <c r="C30" s="53">
+        <f>B30</f>
         <v>1000000</v>
       </c>
-      <c r="D29" s="11">
-        <f t="shared" ref="D29:E29" si="10">C29</f>
+      <c r="D30" s="53">
+        <f t="shared" ref="D30:E30" si="10">C30</f>
         <v>1000000</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E30" s="53">
         <f t="shared" si="10"/>
         <v>1000000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B31" s="80">
         <v>1309246</v>
       </c>
-      <c r="C30" s="11">
-        <f>B30+'Income statement '!C22</f>
+      <c r="C31" s="53">
+        <f>B31+'Income statement '!C22</f>
         <v>2106121</v>
       </c>
-      <c r="D30" s="11">
-        <f>C30+'Income statement '!D22</f>
+      <c r="D31" s="53">
+        <f>C31+'Income statement '!D22</f>
         <v>3242839.75</v>
       </c>
-      <c r="E30" s="11">
-        <f>D30+'Income statement '!E22</f>
+      <c r="E31" s="53">
+        <f>D31+'Income statement '!E22</f>
         <v>4804363.1875</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    <row r="32" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="6">
-        <f>SUM(B29:B30)</f>
+      <c r="B32" s="38">
+        <f>SUM(B30:B31)</f>
         <v>2309246</v>
       </c>
-      <c r="C31" s="11">
-        <f>SUM(C29:C30)</f>
+      <c r="C32" s="60">
+        <f>SUM(C30:C31)</f>
         <v>3106121</v>
       </c>
-      <c r="D31" s="11">
-        <f t="shared" ref="D31:E31" si="11">SUM(D29:D30)</f>
+      <c r="D32" s="60">
+        <f t="shared" ref="D32:E32" si="11">SUM(D30:D31)</f>
         <v>4242839.75</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E32" s="60">
         <f t="shared" si="11"/>
         <v>5804363.1875</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+    <row r="33" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="10">
-        <f>B26+B31</f>
+      <c r="B33" s="48">
+        <f>B27+B32</f>
         <v>3016438</v>
       </c>
-      <c r="C32" s="12">
-        <f>C26+C31</f>
+      <c r="C33" s="58">
+        <f>C27+C32</f>
         <v>3833860.7260273974</v>
       </c>
-      <c r="D32" s="12">
-        <f t="shared" ref="D32:E32" si="12">D26+D31</f>
+      <c r="D33" s="58">
+        <f t="shared" ref="D33:E33" si="12">D27+D32</f>
         <v>4996264.4075342463</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E33" s="59">
         <f t="shared" si="12"/>
         <v>6589894.0094178077</v>
       </c>
@@ -2131,512 +2511,1006 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:E2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E1F010-C4FB-4CC3-82AF-6E4EB4905CC1}">
-  <dimension ref="A1:E20"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="67.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="92" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+    </row>
+    <row r="2" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="92"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="92"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="32" t="s">
+      <c r="B5" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="C5" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="D5" s="98" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
+    <row r="6" spans="1:4" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="101"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="99"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="73" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="40">
-        <f>'Income statement '!B11</f>
-        <v>1250000</v>
-      </c>
-      <c r="C5" s="40">
-        <f>'Income statement '!C11</f>
-        <v>1562500</v>
-      </c>
-      <c r="D5" s="40">
-        <f>'Income statement '!D11</f>
-        <v>1953125</v>
-      </c>
-      <c r="E5" s="40">
-        <f>'Income statement '!E11</f>
-        <v>2441406.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B8" s="62">
+        <f>'Income statement '!C22</f>
+        <v>796875</v>
+      </c>
+      <c r="C8" s="62">
+        <f>'Income statement '!D22</f>
+        <v>1136718.75</v>
+      </c>
+      <c r="D8" s="62">
+        <f>'Income statement '!E22</f>
+        <v>1561523.4375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="40">
-        <f>'Income statement '!B7</f>
-        <v>5000000</v>
-      </c>
-      <c r="C6" s="40">
-        <f>'Income statement '!C7</f>
-        <v>6250000</v>
-      </c>
-      <c r="D6" s="40">
-        <f>'Income statement '!D7</f>
-        <v>7812500</v>
-      </c>
-      <c r="E6" s="40">
-        <f>'Income statement '!E7</f>
-        <v>9765625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B9" s="53">
+        <f>'Income statement '!C17</f>
+        <v>100000</v>
+      </c>
+      <c r="C9" s="53">
+        <f>'Income statement '!D17</f>
+        <v>100000</v>
+      </c>
+      <c r="D9" s="53">
+        <f>'Income statement '!E17</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B10" s="53">
+        <f>'Balance sheet '!B9-'Balance sheet '!C9</f>
+        <v>-154109.94520547939</v>
+      </c>
+      <c r="C10" s="53">
+        <f>'Balance sheet '!C9-'Balance sheet '!D9</f>
+        <v>-192636.98630136985</v>
+      </c>
+      <c r="D10" s="53">
+        <f>'Balance sheet '!D9-'Balance sheet '!E9</f>
+        <v>-240796.23287671257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="67">
+        <f>'Balance sheet '!C21-'Balance sheet '!B21</f>
+        <v>20547.726027397264</v>
+      </c>
+      <c r="C11" s="67">
+        <f>'Balance sheet '!D21-'Balance sheet '!C21</f>
+        <v>25684.931506849302</v>
+      </c>
+      <c r="D11" s="67">
+        <f>'Balance sheet '!E21-'Balance sheet '!D21</f>
+        <v>32106.164383561641</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="25">
+        <f>SUM(B8:B11)</f>
+        <v>763312.78082191781</v>
+      </c>
+      <c r="C12" s="25">
+        <f t="shared" ref="C12:D12" si="0">SUM(C8:C11)</f>
+        <v>1069766.6952054794</v>
+      </c>
+      <c r="D12" s="25">
+        <f t="shared" si="0"/>
+        <v>1452833.3690068491</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="69" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="64">
         <v>0</v>
       </c>
-      <c r="C7" s="40">
-        <v>123288</v>
-      </c>
-      <c r="D7" s="40">
-        <v>-102739</v>
-      </c>
-      <c r="E7" s="40">
-        <v>-128425</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="41">
-        <f>SUM(B5:B7)</f>
-        <v>6250000</v>
-      </c>
-      <c r="C8" s="41">
-        <f>SUM(C5:C7)</f>
-        <v>7935788</v>
-      </c>
-      <c r="D8" s="41">
-        <f>SUM(D5:D7)</f>
-        <v>9662886</v>
-      </c>
-      <c r="E8" s="41">
-        <f>SUM(E5:E7)</f>
-        <v>12078606.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="40">
+      <c r="C15" s="55">
         <v>0</v>
       </c>
-      <c r="C11" s="40">
+      <c r="D15" s="55">
         <v>0</v>
       </c>
-      <c r="D11" s="40">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="24">
+        <f>B15</f>
         <v>0</v>
       </c>
-      <c r="E11" s="40">
+      <c r="C16" s="24">
+        <f t="shared" ref="C16:D16" si="1">C15</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="56">
+      <c r="D16" s="24">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C12" s="56">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="64">
         <v>0</v>
       </c>
-      <c r="D12" s="56">
+      <c r="C19" s="64">
         <v>0</v>
       </c>
-      <c r="E12" s="56">
+      <c r="D19" s="64">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="40">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="24">
+        <f>B19</f>
         <v>0</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C20" s="24">
+        <f t="shared" ref="C20:D20" si="2">C19</f>
         <v>0</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D20" s="24">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E15" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="56">
-        <v>0</v>
-      </c>
-      <c r="C16" s="56">
-        <v>0</v>
-      </c>
-      <c r="D16" s="56">
-        <v>0</v>
-      </c>
-      <c r="E16" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="42">
-        <f>B8+B12+B16</f>
-        <v>6250000</v>
-      </c>
-      <c r="C18" s="42">
-        <f>C8+C12+C16</f>
-        <v>7935788</v>
-      </c>
-      <c r="D18" s="42">
-        <f>D8+D12+D16</f>
-        <v>9662886</v>
-      </c>
-      <c r="E18" s="42">
-        <f>E8+E12+E16</f>
-        <v>12078606.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="40">
-        <v>0</v>
-      </c>
-      <c r="C19" s="40">
-        <f>B20</f>
-        <v>6250000</v>
-      </c>
-      <c r="D19" s="40">
-        <f>C20</f>
-        <v>14185788</v>
-      </c>
-      <c r="E19" s="40">
-        <f>D20</f>
-        <v>23848674</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="35" t="s">
+      <c r="B22" s="60">
+        <f>B12+B16+B20</f>
+        <v>763312.78082191781</v>
+      </c>
+      <c r="C22" s="60">
+        <f t="shared" ref="C22:D22" si="3">C12+C16+C20</f>
+        <v>1069766.6952054794</v>
+      </c>
+      <c r="D22" s="60">
+        <f t="shared" si="3"/>
+        <v>1452833.3690068491</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="43">
-        <f>B18+B19</f>
-        <v>6250000</v>
-      </c>
-      <c r="C20" s="43">
-        <f>C18+C19</f>
-        <v>14185788</v>
-      </c>
-      <c r="D20" s="43">
-        <f>D18+D19</f>
-        <v>23848674</v>
-      </c>
-      <c r="E20" s="43">
-        <f>E18+E19</f>
-        <v>35927280.25</v>
+      <c r="B23" s="71">
+        <f>'Balance sheet '!B8</f>
+        <v>1500000</v>
+      </c>
+      <c r="C23" s="71">
+        <f>'Balance sheet '!C8</f>
+        <v>2263312.780821918</v>
+      </c>
+      <c r="D23" s="71">
+        <f>'Balance sheet '!D8</f>
+        <v>3333079.476027397</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="58">
+        <f>SUM(B22:B23)</f>
+        <v>2263312.7808219176</v>
+      </c>
+      <c r="C24" s="58">
+        <f t="shared" ref="C24:D24" si="4">SUM(C22:C23)</f>
+        <v>3333079.4760273974</v>
+      </c>
+      <c r="D24" s="59">
+        <f t="shared" si="4"/>
+        <v>4785912.8450342463</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A1:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27EA545A-387F-4AE1-B78E-057214D5B253}">
-  <dimension ref="A1:F19"/>
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="62.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="92" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="92"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="92"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="40">
-        <f>'Income statement '!E6</f>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="53">
+        <f>'Income statement '!C18</f>
+        <v>1112500</v>
+      </c>
+      <c r="C8" s="71">
+        <f>'Income statement '!D18</f>
+        <v>1565625</v>
+      </c>
+      <c r="D8" s="71">
+        <f>'Income statement '!E18</f>
+        <v>2132031.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="61">
+        <f>-'DCF valuation '!B8*Assumptions!$E$13</f>
+        <v>-278125</v>
+      </c>
+      <c r="C9" s="54">
+        <f>-'DCF valuation '!C8*Assumptions!$E$13</f>
+        <v>-391406.25</v>
+      </c>
+      <c r="D9" s="54">
+        <f>-'DCF valuation '!D8*Assumptions!$E$13</f>
+        <v>-533007.8125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="51">
+        <f>SUM(B8:B9)</f>
+        <v>834375</v>
+      </c>
+      <c r="C10" s="51">
+        <f t="shared" ref="C10:D10" si="0">SUM(C8:C9)</f>
+        <v>1174218.75</v>
+      </c>
+      <c r="D10" s="51">
+        <f t="shared" si="0"/>
+        <v>1599023.4375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="53">
+        <f>'Income statement '!C17</f>
+        <v>100000</v>
+      </c>
+      <c r="C11" s="53">
+        <f>'Income statement '!D17</f>
+        <v>100000</v>
+      </c>
+      <c r="D11" s="53">
+        <f>'Income statement '!E17</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="53">
+        <f>Cashflow!B10+Cashflow!B11</f>
+        <v>-133562.21917808213</v>
+      </c>
+      <c r="C12" s="53">
+        <f>Cashflow!C10+Cashflow!C11</f>
+        <v>-166952.05479452055</v>
+      </c>
+      <c r="D12" s="53">
+        <f>Cashflow!D10+Cashflow!D11</f>
+        <v>-208690.06849315093</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="54">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="36">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="36">
+      <c r="C13" s="54">
+        <v>0</v>
+      </c>
+      <c r="D13" s="54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="58">
+        <f>SUM(B10:B13)</f>
+        <v>800812.78082191781</v>
+      </c>
+      <c r="C14" s="58">
+        <f t="shared" ref="C14:D14" si="1">SUM(C10:C13)</f>
+        <v>1107266.6952054794</v>
+      </c>
+      <c r="D14" s="59">
+        <f t="shared" si="1"/>
+        <v>1490333.3690068491</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="56"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="24">
+        <v>1</v>
+      </c>
+      <c r="C16" s="24">
+        <v>2</v>
+      </c>
+      <c r="D16" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="65">
+        <f>1/(1+$C$4)^B16</f>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="C17" s="65">
+        <f t="shared" ref="C17:D17" si="2">1/(1+$C$4)^C16</f>
+        <v>0.82644628099173545</v>
+      </c>
+      <c r="D17" s="65">
+        <f t="shared" si="2"/>
+        <v>0.75131480090157754</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="58">
+        <f>B14*B17</f>
+        <v>728011.61892901617</v>
+      </c>
+      <c r="C18" s="58">
+        <f t="shared" ref="C18:D18" si="3">C14*C17</f>
+        <v>915096.4423185779</v>
+      </c>
+      <c r="D18" s="59">
+        <f t="shared" si="3"/>
+        <v>1119709.5184123581</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="66">
+        <f>SUM(B18:D18)</f>
+        <v>2762817.5796599523</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="23">
+        <f>(D14*(1+C5))/(C4-C5)</f>
+        <v>21929191.001100779</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="23">
+        <f>D17*B22</f>
+        <v>16475725.770924697</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="65"/>
+      <c r="B24" s="65"/>
+    </row>
+    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="57" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="59">
+        <f>B21+B23</f>
+        <v>19238543.350584649</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" s="66">
+        <f>'Balance sheet '!B8</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="60">
+        <f>-'Balance sheet '!B25</f>
+        <v>-625000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="59">
+        <f>SUM(B25:B27)</f>
+        <v>20113543.350584649</v>
+      </c>
+      <c r="I28" s="26"/>
+    </row>
+    <row r="30" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A30" s="103" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="104"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="103"/>
+      <c r="B31" s="29">
+        <f>B25</f>
+        <v>19238543.350584649</v>
+      </c>
+      <c r="C31" s="30">
+        <v>0.02</v>
+      </c>
+      <c r="D31" s="31">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E31" s="30">
+        <v>0.03</v>
+      </c>
+      <c r="F31" s="31">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="G31" s="30">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="102" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="30">
+        <v>0.08</v>
+      </c>
+      <c r="C32" s="32">
+        <f t="dataTable" ref="C32:G36" dt2D="1" dtr="1" r1="C5" r2="C4"/>
+        <v>22986140.245148007</v>
+      </c>
+      <c r="D32" s="32">
+        <v>24922080.627633933</v>
+      </c>
+      <c r="E32" s="32">
+        <v>27245209.086617053</v>
+      </c>
+      <c r="F32" s="32">
+        <v>30084588.314263087</v>
+      </c>
+      <c r="G32" s="33">
+        <v>33633812.348820627</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="102"/>
+      <c r="B33" s="30">
+        <v>0.09</v>
+      </c>
+      <c r="C33" s="32">
+        <v>19586423.134752303</v>
+      </c>
+      <c r="D33" s="32">
+        <v>20964866.849027701</v>
+      </c>
+      <c r="E33" s="32">
+        <v>22573051.182349008</v>
+      </c>
+      <c r="F33" s="32">
+        <v>24473632.667183269</v>
+      </c>
+      <c r="G33" s="32">
+        <v>26754330.448984388</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="102"/>
+      <c r="B34" s="30">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="36">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="44">
-        <v>19238543</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="39">
-        <v>0.02</v>
-      </c>
-      <c r="C14" s="39">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D14" s="39">
-        <v>0.03</v>
-      </c>
-      <c r="E14" s="39">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="F14" s="39">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="39"/>
-      <c r="B15" s="45">
-        <f>ROUND(19238543 * (((1+B$14)/($A15-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-66681164</v>
-      </c>
-      <c r="C15" s="45">
-        <f>ROUND(19238543 * (((1+C$14)/($A15-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-53606426</v>
-      </c>
-      <c r="D15" s="45">
-        <f>ROUND(19238543 * (((1+D$14)/($A15-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-44889934</v>
-      </c>
-      <c r="E15" s="45">
-        <f>ROUND(19238543 * (((1+E$14)/($A15-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-38663868</v>
-      </c>
-      <c r="F15" s="45">
-        <f>ROUND(19238543 * (((1+F$14)/($A15-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-33994319</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="39"/>
-      <c r="B16" s="45">
-        <f>ROUND(19238543 * (((1+B$14)/($A16-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-66681164</v>
-      </c>
-      <c r="C16" s="45">
-        <f>ROUND(19238543 * (((1+C$14)/($A16-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-53606426</v>
-      </c>
-      <c r="D16" s="45">
-        <f>ROUND(19238543 * (((1+D$14)/($A16-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-44889934</v>
-      </c>
-      <c r="E16" s="45">
-        <f>ROUND(19238543 * (((1+E$14)/($A16-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-38663868</v>
-      </c>
-      <c r="F16" s="45">
-        <f>ROUND(19238543 * (((1+F$14)/($A16-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-33994319</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
-      <c r="B17" s="46">
-        <f>ROUND(19238543 * (((1+B$14)/($A17-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-66681164</v>
-      </c>
-      <c r="C17" s="46">
-        <f>ROUND(19238543 * (((1+C$14)/($A17-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-53606426</v>
-      </c>
-      <c r="D17" s="44">
-        <f>ROUND(19238543 * (((1+D$14)/($A17-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-44889934</v>
-      </c>
-      <c r="E17" s="45">
-        <f>ROUND(19238543 * (((1+E$14)/($A17-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-38663868</v>
-      </c>
-      <c r="F17" s="45">
-        <f>ROUND(19238543 * (((1+F$14)/($A17-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-33994319</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
-      <c r="B18" s="46">
-        <f>ROUND(19238543 * (((1+B$14)/($A18-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-66681164</v>
-      </c>
-      <c r="C18" s="46">
-        <f>ROUND(19238543 * (((1+C$14)/($A18-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-53606426</v>
-      </c>
-      <c r="D18" s="46">
-        <f>ROUND(19238543 * (((1+D$14)/($A18-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-44889934</v>
-      </c>
-      <c r="E18" s="45">
-        <f>ROUND(19238543 * (((1+E$14)/($A18-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-38663868</v>
-      </c>
-      <c r="F18" s="45">
-        <f>ROUND(19238543 * (((1+F$14)/($A18-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-33994319</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
-      <c r="B19" s="46">
-        <f>ROUND(19238543 * (((1+B$14)/($A19-B$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-66681164</v>
-      </c>
-      <c r="C19" s="46">
-        <f>ROUND(19238543 * (((1+C$14)/($A19-C$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-53606426</v>
-      </c>
-      <c r="D19" s="46">
-        <f>ROUND(19238543 * (((1+D$14)/($A19-D$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-44889934</v>
-      </c>
-      <c r="E19" s="45">
-        <f>ROUND(19238543 * (((1+E$14)/($A19-E$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-38663868</v>
-      </c>
-      <c r="F19" s="45">
-        <f>ROUND(19238543 * (((1+F$14)/($A19-F$14))/((1+0.03)/(0.1-0.03))), 0)</f>
-        <v>-33994319</v>
+      <c r="C34" s="32">
+        <v>17039113.939417519</v>
+      </c>
+      <c r="D34" s="32">
+        <v>18065514.331295509</v>
+      </c>
+      <c r="E34" s="32">
+        <v>19238543.350584649</v>
+      </c>
+      <c r="F34" s="32">
+        <v>20592038.372841347</v>
+      </c>
+      <c r="G34" s="32">
+        <v>22171115.898807492</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="102"/>
+      <c r="B35" s="30">
+        <v>0.11</v>
+      </c>
+      <c r="C35" s="32">
+        <v>15060002.059532067</v>
+      </c>
+      <c r="D35" s="32">
+        <v>15850582.448615823</v>
+      </c>
+      <c r="E35" s="32">
+        <v>16739985.386335054</v>
+      </c>
+      <c r="F35" s="32">
+        <v>17747975.382416844</v>
+      </c>
+      <c r="G35" s="32">
+        <v>18899963.94936746</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="102"/>
+      <c r="B36" s="30">
+        <v>0.12</v>
+      </c>
+      <c r="C36" s="33">
+        <v>13478564.014504556</v>
+      </c>
+      <c r="D36" s="32">
+        <v>14103871.718337314</v>
+      </c>
+      <c r="E36" s="32">
+        <v>14798658.055929273</v>
+      </c>
+      <c r="F36" s="32">
+        <v>15575183.962649696</v>
+      </c>
+      <c r="G36" s="32">
+        <v>16448775.607710173</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="B30:G30"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C32:G36">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3b7b5138-9ca7-4c32-b23e-779e21f95771" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D051C5E93B3111428F61A92D38168E3F" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e98f92b4cef820588696f0edb7e549d2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3b7b5138-9ca7-4c32-b23e-779e21f95771" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc51a20120548cde2d361a7f865cf147" ns3:_="">
+    <xsd:import namespace="3b7b5138-9ca7-4c32-b23e-779e21f95771"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3b7b5138-9ca7-4c32-b23e-779e21f95771" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB85A0D1-A17F-4344-B8B1-9F302D0651DC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3b7b5138-9ca7-4c32-b23e-779e21f95771"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3F17654-3FB2-47E7-8014-BBF1BE64E10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3b7b5138-9ca7-4c32-b23e-779e21f95771"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90029B3-5F80-4D72-B4AB-6B09424D57CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>